--- a/backend/data/Inflacion mensual.xlsx
+++ b/backend/data/Inflacion mensual.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\.shortcut-targets-by-id\1ftoIZqhxjIK-zxyM2xIG9xFIX4GG9BvJ\DCF\Marketing\Instagram\Scripts Python\App DCF Dani\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\.shortcut-targets-by-id\1ftoIZqhxjIK-zxyM2xIG9xFIX4GG9BvJ\DCF\Claude\dcf-herramientas-web\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C66B3AA-39E1-4A35-810C-6DB92787D2AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C37134-7B1C-451F-A06C-5DB291D7C248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A866A124-5132-442D-9FA5-7268A9FD18A4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A866A124-5132-442D-9FA5-7268A9FD18A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -478,7 +478,9 @@
       <c r="A7" s="3">
         <v>46142</v>
       </c>
-      <c r="B7" s="1"/>
+      <c r="B7" s="1">
+        <v>2.5999999999999999E-2</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="3">

--- a/backend/data/Inflacion mensual.xlsx
+++ b/backend/data/Inflacion mensual.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\.shortcut-targets-by-id\1ftoIZqhxjIK-zxyM2xIG9xFIX4GG9BvJ\DCF\Claude\dcf-herramientas-web\backend\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Mi unidad\DCF\Claude\dcf-herramientas-web\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C37134-7B1C-451F-A06C-5DB291D7C248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{788132A7-E8BA-4C25-A7F4-3F46737938F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A866A124-5132-442D-9FA5-7268A9FD18A4}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A866A124-5132-442D-9FA5-7268A9FD18A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -421,12 +410,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DCC9161-DF8D-425B-8F35-03A47268B722}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.90625" style="2"/>
+    <col min="1" max="1" width="10.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -434,7 +423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>45991</v>
       </c>
@@ -442,7 +431,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>46022</v>
       </c>
@@ -450,7 +439,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>46053</v>
       </c>
@@ -458,7 +447,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>46081</v>
       </c>
@@ -466,7 +455,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>46112</v>
       </c>
@@ -474,7 +463,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>46142</v>
       </c>
@@ -482,49 +471,51 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>46173</v>
       </c>
-      <c r="B8" s="1"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B8" s="1">
+        <v>2.1000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>46203</v>
       </c>
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>46234</v>
       </c>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>46265</v>
       </c>
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>46295</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>46326</v>
       </c>
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>46356</v>
       </c>
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>46387</v>
       </c>
